--- a/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>APLS</t>
   </si>
@@ -656,90 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E8" s="3">
         <v>75400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>66600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>250600</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -759,24 +762,27 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E9" s="3">
         <v>5600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,24 +807,27 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>338100</v>
+      </c>
+      <c r="E10" s="3">
         <v>69800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>61400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>225600</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>354400</v>
+      </c>
+      <c r="E12" s="3">
         <v>387200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>420900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>299900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>221000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>105300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>40300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2300</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,39 +961,42 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>32900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>26500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1014,24 +1036,27 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>913700</v>
+      </c>
+      <c r="E17" s="3">
         <v>702900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>703400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>464400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>289500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>127900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-517100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-627500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-636900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-213700</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-50800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,34 +1179,35 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E20" s="3">
         <v>8600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-95900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-99400</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
@@ -1182,30 +1215,33 @@
       <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>100</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-495100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-617300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-731400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-312500</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1218,42 +1254,45 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-11200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E22" s="3">
         <v>32600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,71 +1308,77 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-526500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-651500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-746000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-343000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-304700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-127500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-51000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1345,20 +1390,23 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-528600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-652200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-746400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-344900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-304700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-127500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-51000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-528600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-652200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-746400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-344900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-304700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-127500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-46500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,35 +1716,38 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>95900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>99400</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
@@ -1686,57 +1755,63 @@
       <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>-100</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-528600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-652200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-746400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-344900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-304700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-127500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-51000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-46500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-528600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-652200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-746400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-344900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-304700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-127500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-51000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-46500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,65 +1987,69 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>351200</v>
+      </c>
+      <c r="E41" s="3">
         <v>551800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>640200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>565800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>352000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>176300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>175600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>60400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>311900</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,8 +2065,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1985,63 +2074,69 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E43" s="3">
         <v>29200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>1500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1300</v>
       </c>
       <c r="J43" s="3">
         <v>1300</v>
       </c>
       <c r="K43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E44" s="3">
         <v>85700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2057,8 +2152,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2069,93 +2164,102 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E45" s="3">
         <v>52800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>97100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>39500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>766300</v>
+      </c>
+      <c r="E46" s="3">
         <v>719500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>824000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>917200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>373100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>202400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>182000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5200</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2195,27 +2299,30 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15800</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,21 +2332,24 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,29 +2479,32 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E52" s="3">
         <v>15800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>31600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2394,20 +2513,23 @@
         <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>788700</v>
+      </c>
+      <c r="E54" s="3">
         <v>760200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>881800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>960600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>389200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>203500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,71 +2655,75 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E57" s="3">
         <v>37300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3700</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2500</v>
       </c>
       <c r="K57" s="3">
         <v>2500</v>
       </c>
       <c r="L57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E58" s="3">
         <v>29500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,120 +2739,129 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E59" s="3">
         <v>100800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>107400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>300</v>
       </c>
       <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>300</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E60" s="3">
         <v>167600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>131800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>128300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>17000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>332900</v>
+      </c>
+      <c r="E61" s="3">
         <v>408400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>534200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>358800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>142600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2735,32 +2877,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E62" s="3">
         <v>14400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>17100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>268900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>146700</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>200</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>594200</v>
+      </c>
+      <c r="E66" s="3">
         <v>590300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>683100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>756000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>355000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>42600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3072,26 +3239,29 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>92100</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>77200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>35900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>17000</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2837500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2308900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1656700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-926300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-581500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-276800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-149300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-98300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-71100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E76" s="3">
         <v>169900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>198700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>204600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>148900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-68300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-42200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-22700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-12500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-528600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-652200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-746400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-344900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-304700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-127500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-51000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-46500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,26 +3688,27 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3520,21 +3718,24 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-594700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-513700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-563100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-160500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-211100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-131200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-46600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-18900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3400</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,26 +4022,27 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3832,21 +4052,24 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,27 +4154,30 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>59900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>247600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-317000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3958,21 +4187,24 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,71 +4398,77 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>394500</v>
+      </c>
+      <c r="E100" s="3">
         <v>365700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>392200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>692200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>388500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>131900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>197400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>41200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -4237,52 +4485,58 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-88700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>74700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>215100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>175700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>150800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>APLS</t>
   </si>
@@ -744,8 +744,8 @@
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -772,22 +772,22 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>58500</v>
+        <v>412900</v>
       </c>
       <c r="E9" s="3">
-        <v>5600</v>
+        <v>392900</v>
       </c>
       <c r="F9" s="3">
-        <v>5200</v>
+        <v>426100</v>
       </c>
       <c r="G9" s="3">
         <v>25100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
+      <c r="H9" s="3">
+        <v>221000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>105300</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -817,22 +817,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>338100</v>
+        <v>-16300</v>
       </c>
       <c r="E10" s="3">
-        <v>69800</v>
+        <v>-317500</v>
       </c>
       <c r="F10" s="3">
-        <v>61400</v>
+        <v>-359500</v>
       </c>
       <c r="G10" s="3">
         <v>225600</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
+      <c r="H10" s="3">
+        <v>-221000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-105300</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -970,8 +970,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>32900</v>
@@ -988,8 +988,8 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,19 +1016,19 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1080,16 +1080,16 @@
         <v>913700</v>
       </c>
       <c r="E17" s="3">
-        <v>702900</v>
+        <v>670000</v>
       </c>
       <c r="F17" s="3">
-        <v>703400</v>
+        <v>602800</v>
       </c>
       <c r="G17" s="3">
         <v>464400</v>
       </c>
       <c r="H17" s="3">
-        <v>289500</v>
+        <v>288000</v>
       </c>
       <c r="I17" s="3">
         <v>127900</v>
@@ -1125,19 +1125,19 @@
         <v>-517100</v>
       </c>
       <c r="E18" s="3">
-        <v>-627500</v>
+        <v>-594600</v>
       </c>
       <c r="F18" s="3">
-        <v>-636900</v>
+        <v>-536300</v>
       </c>
       <c r="G18" s="3">
         <v>-213700</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
+      <c r="H18" s="3">
+        <v>-288000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-127900</v>
       </c>
       <c r="J18" s="3">
         <v>-50800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>20200</v>
+        <v>700</v>
       </c>
       <c r="E20" s="3">
-        <v>8600</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>-95900</v>
+        <v>96300</v>
       </c>
       <c r="G20" s="3">
-        <v>-99400</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+        <v>103500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-495100</v>
+        <v>-516100</v>
       </c>
       <c r="E21" s="3">
-        <v>-617300</v>
+        <v>-593300</v>
       </c>
       <c r="F21" s="3">
-        <v>-731400</v>
+        <v>-631200</v>
       </c>
       <c r="G21" s="3">
-        <v>-312500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-316600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-302800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-50900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1293,8 +1293,8 @@
       <c r="I22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>400</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1380,11 +1380,11 @@
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-20200</v>
+        <v>-700</v>
       </c>
       <c r="E32" s="3">
-        <v>-8600</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>95900</v>
+        <v>-96300</v>
       </c>
       <c r="G32" s="3">
-        <v>99400</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+        <v>-103500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -2038,26 +2038,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>4400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F42" s="3">
-        <v>60400</v>
+        <v>61000</v>
       </c>
       <c r="G42" s="3">
         <v>311900</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2087,19 +2087,19 @@
         <v>224500</v>
       </c>
       <c r="E43" s="3">
-        <v>29200</v>
+        <v>37900</v>
       </c>
       <c r="F43" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>80100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>25000</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>1500</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>1300</v>
@@ -2129,13 +2129,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>146400</v>
+        <v>162700</v>
       </c>
       <c r="E44" s="3">
-        <v>85700</v>
+        <v>99700</v>
       </c>
       <c r="F44" s="3">
-        <v>16300</v>
+        <v>24000</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>44300</v>
+        <v>13900</v>
       </c>
       <c r="E45" s="3">
-        <v>52800</v>
+        <v>15200</v>
       </c>
       <c r="F45" s="3">
-        <v>97100</v>
+        <v>12000</v>
       </c>
       <c r="G45" s="3">
-        <v>39500</v>
+        <v>9900</v>
       </c>
       <c r="H45" s="3">
-        <v>21100</v>
+        <v>19400</v>
       </c>
       <c r="I45" s="3">
-        <v>24700</v>
+        <v>24900</v>
       </c>
       <c r="J45" s="3">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="K45" s="3">
         <v>1200</v>
@@ -2263,26 +2263,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2323,8 +2323,8 @@
       <c r="H48" s="3">
         <v>15800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>1000</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -2492,19 +2492,19 @@
         <v>1300</v>
       </c>
       <c r="E52" s="3">
-        <v>15800</v>
+        <v>800</v>
       </c>
       <c r="F52" s="3">
-        <v>31600</v>
+        <v>1600</v>
       </c>
       <c r="G52" s="3">
-        <v>18900</v>
+        <v>900</v>
       </c>
       <c r="H52" s="3">
         <v>400</v>
       </c>
       <c r="I52" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>75800</v>
+        <v>6400</v>
       </c>
       <c r="E58" s="3">
-        <v>29500</v>
+        <v>5600</v>
       </c>
       <c r="F58" s="3">
-        <v>7600</v>
+        <v>4100</v>
       </c>
       <c r="G58" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+        <v>3700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2600</v>
       </c>
       <c r="I58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>134200</v>
+        <v>75800</v>
       </c>
       <c r="E59" s="3">
-        <v>100800</v>
+        <v>29500</v>
       </c>
       <c r="F59" s="3">
-        <v>107400</v>
+        <v>7600</v>
       </c>
       <c r="G59" s="3">
-        <v>115600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>57400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2900</v>
+        <v>4200</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>1100</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>332900</v>
+        <v>104500</v>
       </c>
       <c r="E61" s="3">
-        <v>408400</v>
+        <v>107100</v>
       </c>
       <c r="F61" s="3">
-        <v>534200</v>
+        <v>206100</v>
       </c>
       <c r="G61" s="3">
-        <v>358800</v>
+        <v>374000</v>
       </c>
       <c r="H61" s="3">
-        <v>142600</v>
+        <v>154400</v>
       </c>
       <c r="I61" s="3">
         <v>25400</v>
@@ -2887,19 +2887,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>13800</v>
+        <v>242100</v>
       </c>
       <c r="E62" s="3">
-        <v>14400</v>
+        <v>315600</v>
       </c>
       <c r="F62" s="3">
-        <v>17100</v>
+        <v>345200</v>
       </c>
       <c r="G62" s="3">
-        <v>268900</v>
+        <v>253600</v>
       </c>
       <c r="H62" s="3">
-        <v>146700</v>
+        <v>134800</v>
       </c>
       <c r="I62" s="3">
         <v>200</v>
@@ -3701,13 +3701,13 @@
         <v>1600</v>
       </c>
       <c r="F83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G83" s="3">
+        <v>900</v>
+      </c>
+      <c r="H83" s="3">
         <v>600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>200</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>APLS</t>
   </si>
@@ -656,99 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>781400</v>
+      </c>
+      <c r="E8" s="3">
         <v>396600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>66600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>250600</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -765,33 +768,36 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>445300</v>
+      </c>
+      <c r="E9" s="3">
         <v>412900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>392900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>426100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>221000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>105300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,33 +816,36 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>336100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-16300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-317500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-359500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>225600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-221000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-105300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>327600</v>
+      </c>
+      <c r="E12" s="3">
         <v>354400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>387200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>420900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>299900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>221000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>105300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>40300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>13700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,42 +980,45 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>32900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>26500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,9 +1028,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1019,44 +1041,47 @@
         <v>1800</v>
       </c>
       <c r="E15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>946300</v>
+      </c>
+      <c r="E17" s="3">
         <v>913700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>670000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>602800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>464400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>288000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>127900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-165000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-517100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-594600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-536300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-213700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-288000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-127900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-50800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,37 +1212,38 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>96300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>103500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1218,87 +1251,93 @@
       <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>100</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-165400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-516100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-593300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-631200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-316600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-302800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-128000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-50900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-11200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E22" s="3">
         <v>29600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>32600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,102 +1350,111 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-196700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-526500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-651500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-746000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-343000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-304700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-127500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-51000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-197900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-528600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-652200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-746400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-344900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-304700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-127500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-51000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-46500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-197900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-528600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-652200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-746400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-344900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-304700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-127500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-46500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,38 +1785,41 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-96300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-103500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15000</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -1758,60 +1827,66 @@
       <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>-100</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-197900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-528600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-652200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-746400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-344900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-304700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-127500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-51000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-46500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-197900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-528600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-652200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-746400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-344900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-304700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-127500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-51000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-46500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,79 +2073,83 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>411300</v>
+      </c>
+      <c r="E41" s="3">
         <v>351200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>551800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>640200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>565800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>352000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>176300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>175600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E42" s="3">
         <v>4400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>61000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>311900</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -2068,8 +2157,8 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2077,69 +2166,75 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>271700</v>
+      </c>
+      <c r="E43" s="3">
         <v>224500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>37900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>80100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>25000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>1300</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>1300</v>
       </c>
       <c r="L43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E44" s="3">
         <v>162700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>99700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2155,8 +2250,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2167,99 +2262,108 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E45" s="3">
         <v>13900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24900</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>789000</v>
+      </c>
+      <c r="E46" s="3">
         <v>766300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>719500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>824000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>917200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>373100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>202400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>182000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5200</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2284,8 +2388,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2302,54 +2406,60 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,29 +2598,32 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -2516,20 +2635,23 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>885100</v>
+      </c>
+      <c r="E54" s="3">
         <v>788700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>760200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>881800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>960600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>389200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>203500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>182100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,79 +2785,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E57" s="3">
         <v>37500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2500</v>
       </c>
       <c r="L57" s="3">
         <v>2500</v>
       </c>
       <c r="M57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2742,129 +2875,138 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>75800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>300</v>
       </c>
       <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>300</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E60" s="3">
         <v>247600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>167600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>131800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>128300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>17000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>463000</v>
+      </c>
+      <c r="E61" s="3">
         <v>104500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>107100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>206100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>374000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>154400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26400</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2880,35 +3022,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E62" s="3">
         <v>242100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>315600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>345200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>253600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>134800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>200</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>656500</v>
+      </c>
+      <c r="E66" s="3">
         <v>594200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>590300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>683100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>756000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>355000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>42600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3242,26 +3409,29 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>92100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>77200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>35900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>17000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3035400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2837500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2308900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1656700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-926300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-581500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-276800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-149300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-13800</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>228500</v>
+      </c>
+      <c r="E76" s="3">
         <v>194500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>169900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>198700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>204600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>161000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>148900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-68300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-42200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-22700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-12500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-197900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-528600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-652200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-746400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-344900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-304700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-127500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-51000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-46500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,8 +3886,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3698,20 +3896,20 @@
         <v>1800</v>
       </c>
       <c r="E83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F83" s="3">
         <v>1600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>600</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,21 +3919,24 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-87900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-594700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-513700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-563100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-160500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-211100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-131200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-46600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-18900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,29 +4242,30 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4055,21 +4275,24 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,30 +4383,33 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>59900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>247600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-317000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4190,21 +4419,24 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,77 +4643,83 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E100" s="3">
         <v>394500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>365700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>392200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>692200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>388500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>131900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>197400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>41200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7200</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4488,55 +4736,61 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-88700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>74700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>215100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>175700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>150800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APLS_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>APLS</t>
   </si>
@@ -656,105 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1003800</v>
+      </c>
+      <c r="E8" s="3">
         <v>781400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>396600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>66600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>250600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -771,36 +774,39 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>398100</v>
+      </c>
+      <c r="E9" s="3">
         <v>445300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>412900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>392900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>426100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>303600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>221000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>105300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,36 +825,39 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>605700</v>
+      </c>
+      <c r="E10" s="3">
         <v>336100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-16300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-317500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-359500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-52900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-221000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-105300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>295900</v>
+      </c>
+      <c r="E12" s="3">
         <v>327600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>354400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>387200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>420900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>221000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>105300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>40300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,45 +999,48 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>32900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100600</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>26500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,57 +1050,63 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E15" s="3">
         <v>1800</v>
       </c>
       <c r="F15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G15" s="3">
         <v>1600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>948400</v>
+      </c>
+      <c r="E17" s="3">
         <v>946300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>913700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>670000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>602800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>464400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>288000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>127900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-165000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-517100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-594600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-536300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-213700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-288000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-127900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-50800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,40 +1245,41 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>96300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>103500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15000</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
@@ -1254,93 +1287,99 @@
       <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>100</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-165400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-516100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-593300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-631200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-316600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-302800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-128000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-50900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-11200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E22" s="3">
         <v>40400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>32600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1353,108 +1392,117 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-196700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-526500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-651500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-746000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-343000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-304700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-127500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-51000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-197900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-528600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-652200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-746400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-344900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-304700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-127500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-51000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-197900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-528600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-652200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-746400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-344900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-304700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-127500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-51000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-46500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,41 +1854,44 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-96300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-103500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15000</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
@@ -1830,63 +1899,69 @@
       <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>-100</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-197900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-528600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-652200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-746400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-344900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-304700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-127500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-51000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-46500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-197900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-528600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-652200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-746400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-344900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-304700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-127500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-51000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-46500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,85 +2159,89 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>466200</v>
+      </c>
+      <c r="E41" s="3">
         <v>411300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>351200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>551800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>640200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>565800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>352000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>176300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>175600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E42" s="3">
         <v>4800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>61000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>311900</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2249,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2169,75 +2258,81 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>369200</v>
+      </c>
+      <c r="E43" s="3">
         <v>271700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>224500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>37900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>80100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>1300</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>1300</v>
       </c>
       <c r="M43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N43" s="3">
         <v>1800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E44" s="3">
         <v>82500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>162700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>99700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>24000</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2253,8 +2348,8 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2265,105 +2360,114 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E45" s="3">
         <v>7800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24900</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1014800</v>
+      </c>
+      <c r="E46" s="3">
         <v>789000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>766300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>719500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>824000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>917200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>373100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>202400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>182000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>38000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5200</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2391,8 +2495,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2409,57 +2513,63 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E48" s="3">
         <v>19000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,32 +2717,35 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E52" s="3">
         <v>77100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -2638,20 +2757,23 @@
         <v>100</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1075300</v>
+      </c>
+      <c r="E54" s="3">
         <v>885100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>788700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>760200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>881800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>960600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>389200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>203500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,85 +2915,89 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E57" s="3">
         <v>38600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>37300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2500</v>
       </c>
       <c r="M57" s="3">
         <v>2500</v>
       </c>
       <c r="N57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100700</v>
+      </c>
+      <c r="E58" s="3">
         <v>6800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2878,138 +3011,147 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>75800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>300</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
+      <c r="P59" s="3">
+        <v>300</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>323600</v>
+      </c>
+      <c r="E60" s="3">
         <v>185500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>247600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>167600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>131800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>128300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>373600</v>
+      </c>
+      <c r="E61" s="3">
         <v>463000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>104500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>107100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>374000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>154400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>26400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3025,38 +3167,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E62" s="3">
         <v>8000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>242100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>315600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>345200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>253600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>134800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>200</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>705100</v>
+      </c>
+      <c r="E66" s="3">
         <v>656500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>594200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>590300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>683100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>756000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>355000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>42600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3412,26 +3579,29 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>92100</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>77200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>35900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>17000</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3013000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3035400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2837500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2308900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1656700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-926300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-581500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-276800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-149300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>370100</v>
+      </c>
+      <c r="E76" s="3">
         <v>228500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>194500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>169900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>198700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>204600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>161000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>148900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-68300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-42200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-22700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-12500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-197900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-528600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-652200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-746400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-344900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-304700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-127500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-51000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-46500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,32 +4084,33 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E83" s="3">
         <v>1800</v>
       </c>
       <c r="F83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>600</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,21 +4120,24 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-87900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-594700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-513700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-563100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-160500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-211100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-131200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-18900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,32 +4462,33 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4278,21 +4498,24 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,33 +4612,36 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>59900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>247600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-317000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,21 +4651,24 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,83 +4888,89 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E100" s="3">
         <v>149200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>394500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>365700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>392200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>692200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>388500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>131900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>197400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>41200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4739,58 +4987,64 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E102" s="3">
         <v>60300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-88700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>74700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>215100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>175700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>150800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
